--- a/Compititor's_Price/Novia_Prices/Novia_Prices_07-04-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_07-04-2026.xlsx
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.roofgiant.com/surface-protection/novia-floorguard/</t>
+          <t>No Link</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">

--- a/Compititor's_Price/Novia_Prices/Novia_Prices_07-04-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_07-04-2026.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£47.38</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£40.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£7.2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£86.4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£7.2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£72.0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£7.2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£19.27</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£5.47</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£5.47</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dropdown Error</t>
+          <t>£86.85</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">

--- a/Compititor's_Price/Novia_Prices/Novia_Prices_07-04-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_07-04-2026.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>£53.31</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>£159.89</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
